--- a/validation.xlsx
+++ b/validation.xlsx
@@ -610,7 +610,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capogrosso2013</t>
+          <t>Capogrosso2013_19340</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -625,74 +625,74 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>7, 8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>12, 13, 14, 15, 16, 17, 18, 19, 177, 178, 179, 180</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>6, 7, 8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 193, 194, 195, 196, 197, 198, 199, 200, 201, 202</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>6, 7, 8</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>NFAS</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>NFAS</t>
@@ -710,7 +710,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>193, 194, 195, 196, 197</t>
+          <t>177, 178, 179, 180</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>193, 194, 195, 196, 197</t>
+          <t>177, 178, 179, 180</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>193, 194, 195, 196, 197</t>
+          <t>177, 178, 179, 180</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capogrosso2013</t>
+          <t>Capogrosso2013_19340</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>NFAS</t>
+          <t>1, 19, 26, 33, 35, 43, 47, 54, 60, 67, 73, 80, 88, 95, 103, 112, 120, 129, 139, 149, 159, 170, 181, 193, 205, 217, 229, 241, 253, 265, 277, 289, 301, 313, 325, 337, 349, 361, 373, 385, 397, 409, 421, 433, 445, 457, 469, 481, 493, 505, 517, 529, 541, 553, 565, 577, 589, 601</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,7 +1666,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capogrosso2013</t>
+          <t>Capogrosso2013_19340</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1676,27 +1676,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19326, 19327, 19328, 19329, 19330, 19331, 19332, 19333, 19334, 19335, 19336, 19337, 19338, 19339, 19340</t>
+          <t>19332, 19333, 19334, 19335, 19336, 19337, 19338, 19339</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19331, 19332, 19333, 19334, 19335</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19331, 19332, 19334</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19331, 19332</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19331, 19336</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19332, 19333, 19334</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Capogrosso2013</t>
+          <t>Capogrosso2013_19340</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1843,27 +1843,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19326, 19327, 19328, 19329, 19330, 19331, 19332, 19333, 19334, 19335, 19336, 19337, 19338, 19339, 19340</t>
+          <t>19334, 19335</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19331, 19332, 19333, 19334, 19335</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19331, 19332, 19334</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19331, 19332</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19331, 19336</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NFAS</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2000,7 +2000,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Capogrosso2013</t>
+          <t>Capogrosso2013_19340</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2010,27 +2010,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19326, 19327, 19328, 19329, 19330, 19331, 19332, 19333, 19334, 19335, 19336, 19337, 19338, 19339, 19340</t>
+          <t>19336, 19337</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19331, 19332, 19333, 19334, 19335</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19331, 19332, 19334</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19331, 19332</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19331, 19336</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>NFAS</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -2160,14 +2160,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19334, 19335</t>
+          <t>19336, 19337</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Capogrosso2013</t>
+          <t>Capogrosso2013_19340</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,27 +2177,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19326, 19327, 19336, 19337, 19338</t>
+          <t>19337, 19338</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19336, 19337</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19336, 19337</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19336, 19337</t>
+          <t>NFAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2327,7 +2327,174 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19336, 19337</t>
+          <t>19337, 19338</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Capogrosso2013_19340</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>19338, 19339</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>NFAS</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>19338, 19339</t>
         </is>
       </c>
     </row>
